--- a/Excel Junior.xlsx
+++ b/Excel Junior.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hani\Documents\Excel-Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{355E6CF7-3D72-4D0E-8443-6335E9B9E48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1937DDD7-BDBC-4667-9623-4B68C2D26F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{3A5B9488-4C2F-4F4D-AD83-87F7C6430F9C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{3A5B9488-4C2F-4F4D-AD83-87F7C6430F9C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data Penjualan" sheetId="1" r:id="rId1"/>
+    <sheet name="Master Produk" sheetId="4" r:id="rId2"/>
+    <sheet name="Data Dashboard" sheetId="2" r:id="rId3"/>
+    <sheet name="Rumus" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,12 +41,526 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="165">
+  <si>
+    <t>DATA PENJUALAN</t>
+  </si>
+  <si>
+    <t>Tanggal</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Produk</t>
+  </si>
+  <si>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Harga</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Diskon</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Total Penjualan</t>
+  </si>
+  <si>
+    <t>Jumlah Transaksi</t>
+  </si>
+  <si>
+    <t>Produk Terlaris</t>
+  </si>
+  <si>
+    <t>Kategori Terlaris</t>
+  </si>
+  <si>
+    <t>Chart</t>
+  </si>
+  <si>
+    <t>21/07/2026</t>
+  </si>
+  <si>
+    <t>INV001</t>
+  </si>
+  <si>
+    <t>Flashdisk Sandisk 32GB</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>INV002</t>
+  </si>
+  <si>
+    <t>Monitor LG 24"</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>INV003</t>
+  </si>
+  <si>
+    <t>Speaker Logitech Z120</t>
+  </si>
+  <si>
+    <t>Audio</t>
+  </si>
+  <si>
+    <t>INV004</t>
+  </si>
+  <si>
+    <t>Mouse Logitech M185</t>
+  </si>
+  <si>
+    <t>Aksesoris</t>
+  </si>
+  <si>
+    <t>INV005</t>
+  </si>
+  <si>
+    <t>UPS 650VA</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t>INV006</t>
+  </si>
+  <si>
+    <t>RAM DDR4 16GB</t>
+  </si>
+  <si>
+    <t>Komponen</t>
+  </si>
+  <si>
+    <t>INV007</t>
+  </si>
+  <si>
+    <t>Router TP-Link</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>26/07/2026</t>
+  </si>
+  <si>
+    <t>INV008</t>
+  </si>
+  <si>
+    <t>INV009</t>
+  </si>
+  <si>
+    <t>Printer Epson L3250</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>INV010</t>
+  </si>
+  <si>
+    <t>Kabel HDMI 2 Meter</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>INV011</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>INV012</t>
+  </si>
+  <si>
+    <t>INV013</t>
+  </si>
+  <si>
+    <t>INV014</t>
+  </si>
+  <si>
+    <t>Webcam Logitech C270</t>
+  </si>
+  <si>
+    <t>19/07/2026</t>
+  </si>
+  <si>
+    <t>INV015</t>
+  </si>
+  <si>
+    <t>INV016</t>
+  </si>
+  <si>
+    <t>28/07/2026</t>
+  </si>
+  <si>
+    <t>INV017</t>
+  </si>
+  <si>
+    <t>INV018</t>
+  </si>
+  <si>
+    <t>INV019</t>
+  </si>
+  <si>
+    <t>Laptop Stand</t>
+  </si>
+  <si>
+    <t>23/07/2026</t>
+  </si>
+  <si>
+    <t>INV020</t>
+  </si>
+  <si>
+    <t>Headset Fantech HG11</t>
+  </si>
+  <si>
+    <t>INV021</t>
+  </si>
+  <si>
+    <t>INV022</t>
+  </si>
+  <si>
+    <t>INV023</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>INV024</t>
+  </si>
+  <si>
+    <t>Keyboard Logitech K120</t>
+  </si>
+  <si>
+    <t>INV025</t>
+  </si>
+  <si>
+    <t>INV026</t>
+  </si>
+  <si>
+    <t>Switch 8 Port</t>
+  </si>
+  <si>
+    <t>INV027</t>
+  </si>
+  <si>
+    <t>24/07/2026</t>
+  </si>
+  <si>
+    <t>INV028</t>
+  </si>
+  <si>
+    <t>INV029</t>
+  </si>
+  <si>
+    <t>Microphone USB</t>
+  </si>
+  <si>
+    <t>INV030</t>
+  </si>
+  <si>
+    <t>INV031</t>
+  </si>
+  <si>
+    <t>INV032</t>
+  </si>
+  <si>
+    <t>RAM DDR4 8GB</t>
+  </si>
+  <si>
+    <t>INV033</t>
+  </si>
+  <si>
+    <t>Cooling Pad</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>INV034</t>
+  </si>
+  <si>
+    <t>INV035</t>
+  </si>
+  <si>
+    <t>25/07/2026</t>
+  </si>
+  <si>
+    <t>INV036</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>INV037</t>
+  </si>
+  <si>
+    <t>INV038</t>
+  </si>
+  <si>
+    <t>INV039</t>
+  </si>
+  <si>
+    <t>INV040</t>
+  </si>
+  <si>
+    <t>INV041</t>
+  </si>
+  <si>
+    <t>INV042</t>
+  </si>
+  <si>
+    <t>INV043</t>
+  </si>
+  <si>
+    <t>INV044</t>
+  </si>
+  <si>
+    <t>INV045</t>
+  </si>
+  <si>
+    <t>INV046</t>
+  </si>
+  <si>
+    <t>INV047</t>
+  </si>
+  <si>
+    <t>INV048</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>INV049</t>
+  </si>
+  <si>
+    <t>INV050</t>
+  </si>
+  <si>
+    <t>INV051</t>
+  </si>
+  <si>
+    <t>INV052</t>
+  </si>
+  <si>
+    <t>INV053</t>
+  </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
+  <si>
+    <t>INV054</t>
+  </si>
+  <si>
+    <t>INV055</t>
+  </si>
+  <si>
+    <t>INV056</t>
+  </si>
+  <si>
+    <t>INV057</t>
+  </si>
+  <si>
+    <t>INV058</t>
+  </si>
+  <si>
+    <t>INV059</t>
+  </si>
+  <si>
+    <t>Harddisk External 1TB</t>
+  </si>
+  <si>
+    <t>INV060</t>
+  </si>
+  <si>
+    <t>INV061</t>
+  </si>
+  <si>
+    <t>INV062</t>
+  </si>
+  <si>
+    <t>INV063</t>
+  </si>
+  <si>
+    <t>INV064</t>
+  </si>
+  <si>
+    <t>INV065</t>
+  </si>
+  <si>
+    <t>INV066</t>
+  </si>
+  <si>
+    <t>30/07/2026</t>
+  </si>
+  <si>
+    <t>INV067</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>INV068</t>
+  </si>
+  <si>
+    <t>INV069</t>
+  </si>
+  <si>
+    <t>INV070</t>
+  </si>
+  <si>
+    <t>INV071</t>
+  </si>
+  <si>
+    <t>INV072</t>
+  </si>
+  <si>
+    <t>INV073</t>
+  </si>
+  <si>
+    <t>INV074</t>
+  </si>
+  <si>
+    <t>INV075</t>
+  </si>
+  <si>
+    <t>INV076</t>
+  </si>
+  <si>
+    <t>INV077</t>
+  </si>
+  <si>
+    <t>Mousepad Gaming</t>
+  </si>
+  <si>
+    <t>INV078</t>
+  </si>
+  <si>
+    <t>INV079</t>
+  </si>
+  <si>
+    <t>INV080</t>
+  </si>
+  <si>
+    <t>INV081</t>
+  </si>
+  <si>
+    <t>INV082</t>
+  </si>
+  <si>
+    <t>INV083</t>
+  </si>
+  <si>
+    <t>INV084</t>
+  </si>
+  <si>
+    <t>INV085</t>
+  </si>
+  <si>
+    <t>INV086</t>
+  </si>
+  <si>
+    <t>INV087</t>
+  </si>
+  <si>
+    <t>INV088</t>
+  </si>
+  <si>
+    <t>INV089</t>
+  </si>
+  <si>
+    <t>INV090</t>
+  </si>
+  <si>
+    <t>INV091</t>
+  </si>
+  <si>
+    <t>SSD Kingston 512GB</t>
+  </si>
+  <si>
+    <t>INV092</t>
+  </si>
+  <si>
+    <t>INV093</t>
+  </si>
+  <si>
+    <t>INV094</t>
+  </si>
+  <si>
+    <t>INV095</t>
+  </si>
+  <si>
+    <t>INV096</t>
+  </si>
+  <si>
+    <t>INV097</t>
+  </si>
+  <si>
+    <t>INV098</t>
+  </si>
+  <si>
+    <t>INV099</t>
+  </si>
+  <si>
+    <t>INV100</t>
+  </si>
+  <si>
+    <t>Daftar Produk</t>
+  </si>
+  <si>
+    <t>Kode Produk</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -69,8 +586,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,6 +933,3125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4651C7BD-847F-40A8-9C06-4B2E5CE47DC4}">
+  <dimension ref="B3:L106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L7" s="3">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E8" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3695000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L9" s="3">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E10" s="4">
+        <v>46060</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="3">
+        <v>125000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L10" s="3">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E11" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3">
+        <v>720000</v>
+      </c>
+      <c r="J11" s="3">
+        <v>5</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3425000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E13" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3">
+        <v>420000</v>
+      </c>
+      <c r="J13" s="3">
+        <v>5</v>
+      </c>
+      <c r="K13" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L13" s="3">
+        <v>2080000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="3">
+        <v>125000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L14" s="3">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E15" s="4">
+        <v>46333</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L15" s="3">
+        <v>4885000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L16" s="3">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L17" s="3">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>1</v>
+      </c>
+      <c r="K18" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L18" s="3">
+        <v>2350000</v>
+      </c>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J19" s="3">
+        <v>4</v>
+      </c>
+      <c r="K19" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L19" s="3">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I20" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1725000</v>
+      </c>
+    </row>
+    <row r="21" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>695000</v>
+      </c>
+    </row>
+    <row r="22" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>5545000</v>
+      </c>
+    </row>
+    <row r="23" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="24" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E24" s="4">
+        <v>46272</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="3">
+        <v>420000</v>
+      </c>
+      <c r="J24" s="3">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="25" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E25" s="4">
+        <v>46363</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="3">
+        <v>220000</v>
+      </c>
+      <c r="J25" s="3">
+        <v>2</v>
+      </c>
+      <c r="K25" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L25" s="3">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="26" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="3">
+        <v>275000</v>
+      </c>
+      <c r="J26" s="3">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1365000</v>
+      </c>
+    </row>
+    <row r="27" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J27" s="3">
+        <v>2</v>
+      </c>
+      <c r="K27" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L27" s="3">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="28" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J28" s="3">
+        <v>5</v>
+      </c>
+      <c r="K28" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L28" s="3">
+        <v>12235000</v>
+      </c>
+    </row>
+    <row r="29" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I29" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L29" s="3">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="30" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J30" s="3">
+        <v>3</v>
+      </c>
+      <c r="K30" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L30" s="3">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E31" s="4">
+        <v>46272</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="3">
+        <v>275000</v>
+      </c>
+      <c r="J31" s="3">
+        <v>2</v>
+      </c>
+      <c r="K31" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L31" s="3">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="32" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E32" s="4">
+        <v>46210</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I32" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>4</v>
+      </c>
+      <c r="K32" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1460000</v>
+      </c>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E33" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2</v>
+      </c>
+      <c r="K33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L33" s="3">
+        <v>4885000</v>
+      </c>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J34" s="3">
+        <v>5</v>
+      </c>
+      <c r="K34" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L34" s="3">
+        <v>1030000</v>
+      </c>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E35" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="3">
+        <v>460000</v>
+      </c>
+      <c r="J35" s="3">
+        <v>4</v>
+      </c>
+      <c r="K35" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1790000</v>
+      </c>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E36" s="4">
+        <v>46363</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J36" s="3">
+        <v>2</v>
+      </c>
+      <c r="K36" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L36" s="3">
+        <v>3600000</v>
+      </c>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E37" s="4">
+        <v>46088</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J37" s="3">
+        <v>1</v>
+      </c>
+      <c r="K37" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L37" s="3">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="3">
+        <v>385000</v>
+      </c>
+      <c r="J38" s="3">
+        <v>4</v>
+      </c>
+      <c r="K38" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L38" s="3">
+        <v>1535000</v>
+      </c>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I39" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J39" s="3">
+        <v>5</v>
+      </c>
+      <c r="K39" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L39" s="3">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J40" s="3">
+        <v>5</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3">
+        <v>12250000</v>
+      </c>
+    </row>
+    <row r="41" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I41" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J41" s="3">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L41" s="3">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="42" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1</v>
+      </c>
+      <c r="K42" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L42" s="3">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="43" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I43" s="3">
+        <v>385000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>4</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>1540000</v>
+      </c>
+    </row>
+    <row r="44" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L44" s="3">
+        <v>12240000</v>
+      </c>
+    </row>
+    <row r="45" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L45" s="3">
+        <v>270000</v>
+      </c>
+    </row>
+    <row r="46" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E46" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="3">
+        <v>220000</v>
+      </c>
+      <c r="J46" s="3">
+        <v>2</v>
+      </c>
+      <c r="K46" s="3">
+        <v>0</v>
+      </c>
+      <c r="L46" s="3">
+        <v>440000</v>
+      </c>
+    </row>
+    <row r="47" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I47" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>4</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="48" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E48" s="4">
+        <v>46119</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" s="3">
+        <v>220000</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L48" s="3">
+        <v>645000</v>
+      </c>
+    </row>
+    <row r="49" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E49" s="4">
+        <v>46060</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J49" s="3">
+        <v>5</v>
+      </c>
+      <c r="K49" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L49" s="3">
+        <v>9245000</v>
+      </c>
+    </row>
+    <row r="50" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E50" s="4">
+        <v>46088</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I50" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1</v>
+      </c>
+      <c r="K50" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L50" s="3">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="51" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E51" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I51" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J51" s="3">
+        <v>5</v>
+      </c>
+      <c r="K51" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L51" s="3">
+        <v>1940000</v>
+      </c>
+    </row>
+    <row r="52" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E52" s="4">
+        <v>46272</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="3">
+        <v>720000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L52" s="3">
+        <v>3550000</v>
+      </c>
+    </row>
+    <row r="53" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I53" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J53" s="3">
+        <v>5</v>
+      </c>
+      <c r="K53" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L53" s="3">
+        <v>3460000</v>
+      </c>
+    </row>
+    <row r="54" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E54" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I54" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J54" s="3">
+        <v>4</v>
+      </c>
+      <c r="K54" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L54" s="3">
+        <v>1375000</v>
+      </c>
+    </row>
+    <row r="55" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E55" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="3">
+        <v>720000</v>
+      </c>
+      <c r="J55" s="3">
+        <v>4</v>
+      </c>
+      <c r="K55" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L55" s="3">
+        <v>2875000</v>
+      </c>
+    </row>
+    <row r="56" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E56" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1</v>
+      </c>
+      <c r="K56" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L56" s="3">
+        <v>1825000</v>
+      </c>
+    </row>
+    <row r="57" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E57" s="4">
+        <v>46029</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I57" s="3">
+        <v>460000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2285000</v>
+      </c>
+    </row>
+    <row r="58" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E58" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1</v>
+      </c>
+      <c r="K58" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L58" s="3">
+        <v>1845000</v>
+      </c>
+    </row>
+    <row r="59" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E59" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I59" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2</v>
+      </c>
+      <c r="K59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>355000</v>
+      </c>
+    </row>
+    <row r="60" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E60" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I60" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L60" s="3">
+        <v>535000</v>
+      </c>
+    </row>
+    <row r="61" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E61" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>3</v>
+      </c>
+      <c r="K61" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L61" s="3">
+        <v>5450000</v>
+      </c>
+    </row>
+    <row r="62" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E62" s="4">
+        <v>46210</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I62" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2</v>
+      </c>
+      <c r="K62" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L62" s="3">
+        <v>320000</v>
+      </c>
+    </row>
+    <row r="63" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E63" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I63" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J63" s="3">
+        <v>4</v>
+      </c>
+      <c r="K63" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L63" s="3">
+        <v>1545000</v>
+      </c>
+    </row>
+    <row r="64" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E64" s="4">
+        <v>46119</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I64" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4</v>
+      </c>
+      <c r="K64" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L64" s="3">
+        <v>355000</v>
+      </c>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E65" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I65" s="3">
+        <v>950000</v>
+      </c>
+      <c r="J65" s="3">
+        <v>4</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>3800000</v>
+      </c>
+    </row>
+    <row r="66" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I66" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J66" s="3">
+        <v>1</v>
+      </c>
+      <c r="K66" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L66" s="3">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="67" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E67" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I67" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1</v>
+      </c>
+      <c r="K67" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L67" s="3">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="68" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E68" s="4">
+        <v>46210</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I68" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J68" s="3">
+        <v>5</v>
+      </c>
+      <c r="K68" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L68" s="3">
+        <v>3375000</v>
+      </c>
+    </row>
+    <row r="69" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E69" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I69" s="3">
+        <v>950000</v>
+      </c>
+      <c r="J69" s="3">
+        <v>2</v>
+      </c>
+      <c r="K69" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L69" s="3">
+        <v>1880000</v>
+      </c>
+    </row>
+    <row r="70" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E70" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I70" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1</v>
+      </c>
+      <c r="K70" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L70" s="3">
+        <v>1750000</v>
+      </c>
+    </row>
+    <row r="71" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E71" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I71" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="72" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1</v>
+      </c>
+      <c r="K72" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L72" s="3">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="73" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E73" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I73" s="3">
+        <v>1850000</v>
+      </c>
+      <c r="J73" s="3">
+        <v>2</v>
+      </c>
+      <c r="K73" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L73" s="3">
+        <v>3650000</v>
+      </c>
+    </row>
+    <row r="74" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E74" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I74" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J74" s="3">
+        <v>2</v>
+      </c>
+      <c r="K74" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L74" s="3">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="75" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E75" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I75" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J75" s="3">
+        <v>2</v>
+      </c>
+      <c r="K75" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L75" s="3">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="76" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E76" s="4">
+        <v>46029</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I76" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L76" s="3">
+        <v>440000</v>
+      </c>
+    </row>
+    <row r="77" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E77" s="4">
+        <v>46302</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I77" s="3">
+        <v>950000</v>
+      </c>
+      <c r="J77" s="3">
+        <v>5</v>
+      </c>
+      <c r="K77" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L77" s="3">
+        <v>4650000</v>
+      </c>
+    </row>
+    <row r="78" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E78" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J78" s="3">
+        <v>3</v>
+      </c>
+      <c r="K78" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L78" s="3">
+        <v>2070000</v>
+      </c>
+    </row>
+    <row r="79" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I79" s="3">
+        <v>180000</v>
+      </c>
+      <c r="J79" s="3">
+        <v>5</v>
+      </c>
+      <c r="K79" s="3">
+        <v>0</v>
+      </c>
+      <c r="L79" s="3">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="80" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E80" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I80" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1</v>
+      </c>
+      <c r="K80" s="3">
+        <v>0</v>
+      </c>
+      <c r="L80" s="3">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="81" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E81" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I81" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J81" s="3">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L81" s="3">
+        <v>1940000</v>
+      </c>
+    </row>
+    <row r="82" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E82" s="4">
+        <v>46060</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I82" s="3">
+        <v>720000</v>
+      </c>
+      <c r="J82" s="3">
+        <v>1</v>
+      </c>
+      <c r="K82" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L82" s="3">
+        <v>710000</v>
+      </c>
+    </row>
+    <row r="83" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E83" s="4">
+        <v>46088</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I83" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>1</v>
+      </c>
+      <c r="K83" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="84" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I84" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J84" s="3">
+        <v>5</v>
+      </c>
+      <c r="K84" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L84" s="3">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="85" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E85" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I85" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J85" s="3">
+        <v>1</v>
+      </c>
+      <c r="K85" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L85" s="3">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="86" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86" s="3">
+        <v>460000</v>
+      </c>
+      <c r="J86" s="3">
+        <v>5</v>
+      </c>
+      <c r="K86" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L86" s="3">
+        <v>2275000</v>
+      </c>
+    </row>
+    <row r="87" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E87" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I87" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J87" s="3">
+        <v>2</v>
+      </c>
+      <c r="K87" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L87" s="3">
+        <v>4875000</v>
+      </c>
+    </row>
+    <row r="88" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E88" s="4">
+        <v>46241</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I88" s="3">
+        <v>2450000</v>
+      </c>
+      <c r="J88" s="3">
+        <v>4</v>
+      </c>
+      <c r="K88" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L88" s="3">
+        <v>9790000</v>
+      </c>
+    </row>
+    <row r="89" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I89" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>4</v>
+      </c>
+      <c r="K89" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L89" s="3">
+        <v>1375000</v>
+      </c>
+    </row>
+    <row r="90" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E90" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I90" s="3">
+        <v>275000</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1</v>
+      </c>
+      <c r="K90" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L90" s="3">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="91" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E91" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I91" s="3">
+        <v>460000</v>
+      </c>
+      <c r="J91" s="3">
+        <v>1</v>
+      </c>
+      <c r="K91" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L91" s="3">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="92" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I92" s="3">
+        <v>695000</v>
+      </c>
+      <c r="J92" s="3">
+        <v>5</v>
+      </c>
+      <c r="K92" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L92" s="3">
+        <v>3455000</v>
+      </c>
+    </row>
+    <row r="93" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E93" s="4">
+        <v>46149</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I93" s="3">
+        <v>220000</v>
+      </c>
+      <c r="J93" s="3">
+        <v>1</v>
+      </c>
+      <c r="K93" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L93" s="3">
+        <v>205000</v>
+      </c>
+    </row>
+    <row r="94" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E94" s="4">
+        <v>46363</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>2</v>
+      </c>
+      <c r="K94" s="3">
+        <v>100000</v>
+      </c>
+      <c r="L94" s="3">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="95" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E95" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I95" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J95" s="3">
+        <v>3</v>
+      </c>
+      <c r="K95" s="3">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="96" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I96" s="3">
+        <v>210000</v>
+      </c>
+      <c r="J96" s="3">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L96" s="3">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="97" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" s="3">
+        <v>725000</v>
+      </c>
+      <c r="J97" s="3">
+        <v>3</v>
+      </c>
+      <c r="K97" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L97" s="3">
+        <v>2170000</v>
+      </c>
+    </row>
+    <row r="98" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E98" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" s="3">
+        <v>95000</v>
+      </c>
+      <c r="J98" s="3">
+        <v>5</v>
+      </c>
+      <c r="K98" s="3">
+        <v>10000</v>
+      </c>
+      <c r="L98" s="3">
+        <v>465000</v>
+      </c>
+    </row>
+    <row r="99" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E99" s="4">
+        <v>46272</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I99" s="3">
+        <v>350000</v>
+      </c>
+      <c r="J99" s="3">
+        <v>5</v>
+      </c>
+      <c r="K99" s="3">
+        <v>15000</v>
+      </c>
+      <c r="L99" s="3">
+        <v>1735000</v>
+      </c>
+    </row>
+    <row r="100" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E100" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I100" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J100" s="3">
+        <v>2</v>
+      </c>
+      <c r="K100" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L100" s="3">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="101" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E101" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I101" s="3">
+        <v>390000</v>
+      </c>
+      <c r="J101" s="3">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>1170000</v>
+      </c>
+    </row>
+    <row r="102" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E102" s="4">
+        <v>46088</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" s="3">
+        <v>950000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>3</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="103" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E103" s="4">
+        <v>46029</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I103" s="3">
+        <v>85000</v>
+      </c>
+      <c r="J103" s="3">
+        <v>2</v>
+      </c>
+      <c r="K103" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L103" s="3">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="104" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E104" s="4">
+        <v>46180</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I104" s="3">
+        <v>420000</v>
+      </c>
+      <c r="J104" s="3">
+        <v>5</v>
+      </c>
+      <c r="K104" s="3">
+        <v>50000</v>
+      </c>
+      <c r="L104" s="3">
+        <v>2050000</v>
+      </c>
+    </row>
+    <row r="105" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E105" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I105" s="3">
+        <v>125000</v>
+      </c>
+      <c r="J105" s="3">
+        <v>1</v>
+      </c>
+      <c r="K105" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L105" s="3">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="106" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E106" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" s="3">
+        <v>725000</v>
+      </c>
+      <c r="J106" s="3">
+        <v>5</v>
+      </c>
+      <c r="K106" s="3">
+        <v>0</v>
+      </c>
+      <c r="L106" s="3">
+        <v>3625000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D745B554-E764-447C-AC09-23805B76D7ED}">
+  <dimension ref="B2:H23"/>
+  <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <f>"PR"&amp;TEXT(ROW()-3,"000")</f>
+        <v>PR001</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" ref="E5:E23" si="0">"PR"&amp;TEXT(ROW()-3,"000")</f>
+        <v>PR002</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="5">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>PR003</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="5">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>4</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>PR004</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="5">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="5">
+        <v>5</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>PR005</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="5">
+        <v>725000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>PR006</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="5">
+        <v>7</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>PR007</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="5">
+        <v>695000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>8</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>PR008</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="5">
+        <v>9</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v>PR009</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="5">
+        <v>2450000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <v>10</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>PR010</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="5">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <v>11</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v>PR011</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="5">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <v>12</v>
+      </c>
+      <c r="E15" t="str">
+        <f t="shared" si="0"/>
+        <v>PR012</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="5">
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <v>13</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" si="0"/>
+        <v>PR013</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="5">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="17" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>14</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v>PR014</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="5">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="18" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <v>15</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>PR015</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="5">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="19" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>16</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>PR016</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="5">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="20" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <v>17</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>PR017</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="5">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="21" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="5">
+        <v>18</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>PR018</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="5">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="22" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="5">
+        <v>19</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>PR019</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="5">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="23" spans="4:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="5">
+        <v>20</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>PR020</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="5">
+        <v>75000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E408928-F670-4389-91FC-A42611E7F6CC}">
+  <dimension ref="B3:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FD5F84-78FA-418E-BD7B-94443E20F540}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Excel Junior.xlsx
+++ b/Excel Junior.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hani\Documents\Excel-Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF3675F-2B4B-45B9-A903-1EBAEB5D2485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE738908-7368-4C2E-B69C-BA70D8364FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{3A5B9488-4C2F-4F4D-AD83-87F7C6430F9C}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="166">
   <si>
     <t>DATA PENJUALAN</t>
   </si>
@@ -1466,11 +1466,13 @@
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
         <v>Mouse Logitech M185</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>19</v>
+      <c r="I6" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J6" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>

--- a/Excel Junior.xlsx
+++ b/Excel Junior.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hani\Documents\Excel-Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE738908-7368-4C2E-B69C-BA70D8364FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C91081-2D7B-4D2C-9170-4C5F1021DDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{3A5B9488-4C2F-4F4D-AD83-87F7C6430F9C}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="185">
   <si>
     <t>DATA PENJUALAN</t>
   </si>
@@ -542,14 +542,71 @@
     <t>Kode Produk</t>
   </si>
   <si>
+    <t>PR004</t>
+  </si>
+  <si>
     <t>PR001</t>
+  </si>
+  <si>
+    <t>PR002</t>
+  </si>
+  <si>
+    <t>PR003</t>
+  </si>
+  <si>
+    <t>PR005</t>
+  </si>
+  <si>
+    <t>PR006</t>
+  </si>
+  <si>
+    <t>PR007</t>
+  </si>
+  <si>
+    <t>PR008</t>
+  </si>
+  <si>
+    <t>PR009</t>
+  </si>
+  <si>
+    <t>PR010</t>
+  </si>
+  <si>
+    <t>PR011</t>
+  </si>
+  <si>
+    <t>PR012</t>
+  </si>
+  <si>
+    <t>PR013</t>
+  </si>
+  <si>
+    <t>PR014</t>
+  </si>
+  <si>
+    <t>PR015</t>
+  </si>
+  <si>
+    <t>PR016</t>
+  </si>
+  <si>
+    <t>PR017</t>
+  </si>
+  <si>
+    <t>PR018</t>
+  </si>
+  <si>
+    <t>PR019</t>
+  </si>
+  <si>
+    <t>PR020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,6 +632,12 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1054,9 +1117,15 @@
     <tableColumn id="2" xr3:uid="{94A413BD-172E-40E6-AF21-1EEEA9EFA759}" name="Tanggal" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{F6F3FC75-2B3D-4B29-9184-A188381B5748}" name="Invoice" dataDxfId="8"/>
     <tableColumn id="4" xr3:uid="{C000D992-1E30-40E9-B271-1CEC88E119C4}" name="Kode Produk"/>
-    <tableColumn id="5" xr3:uid="{C78995F6-9DDB-423C-87DA-9E1F7F2F2350}" name="Produk" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{ED5FAEC4-2BDA-4644-AFC5-A54D20E98610}" name="Kategori" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{CFCC14E9-E4A7-4903-B8EB-DD0E69C2E068}" name="Harga" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{C78995F6-9DDB-423C-87DA-9E1F7F2F2350}" name="Produk" dataDxfId="7">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{ED5FAEC4-2BDA-4644-AFC5-A54D20E98610}" name="Kategori" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{CFCC14E9-E4A7-4903-B8EB-DD0E69C2E068}" name="Harga" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="8" xr3:uid="{D0A2317B-0228-4B19-924B-8C05167BA4AE}" name="Qty" dataDxfId="4"/>
     <tableColumn id="9" xr3:uid="{DD9C52D6-FDB5-46F9-803A-0E083341E491}" name="Diskon" dataDxfId="3"/>
     <tableColumn id="10" xr3:uid="{2809CFFE-8337-4F60-BBEB-44FE115319C6}" name="Total" dataDxfId="2"/>
@@ -1406,7 +1475,7 @@
     <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
     <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1460,7 +1529,7 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H6" s="6" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1495,16 +1564,19 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>22</v>
+        <v>166</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mouse Logitech M185</v>
+      </c>
+      <c r="I7" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J7" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K7" s="6">
         <v>2</v>
@@ -1526,14 +1598,20 @@
       <c r="F8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>26</v>
+      <c r="G8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Flashdisk Sandisk 32GB</v>
+      </c>
+      <c r="I8" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J8" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>95000</v>
       </c>
       <c r="K8" s="6">
         <v>1</v>
@@ -1555,14 +1633,20 @@
       <c r="F9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>29</v>
+      <c r="G9" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I9" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J9" s="6">
-        <v>125000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K9" s="6">
         <v>1</v>
@@ -1584,14 +1668,20 @@
       <c r="F10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>32</v>
+      <c r="G10" t="s">
+        <v>168</v>
+      </c>
+      <c r="H10" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Headset Fantech HG11</v>
+      </c>
+      <c r="I10" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J10" s="6">
-        <v>720000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>275000</v>
       </c>
       <c r="K10" s="6">
         <v>5</v>
@@ -1613,14 +1703,20 @@
       <c r="F11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>36</v>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I11" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J11" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K11" s="6">
         <v>5</v>
@@ -1642,14 +1738,20 @@
       <c r="F12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>39</v>
+      <c r="G12" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I12" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J12" s="6">
-        <v>420000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K12" s="6">
         <v>5</v>
@@ -1671,14 +1773,20 @@
       <c r="F13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>29</v>
+      <c r="G13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I13" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J13" s="6">
-        <v>125000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K13" s="6">
         <v>2</v>
@@ -1700,14 +1808,20 @@
       <c r="F14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>44</v>
+      <c r="G14" t="s">
+        <v>170</v>
+      </c>
+      <c r="H14" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I14" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J14" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K14" s="6">
         <v>2</v>
@@ -1729,14 +1843,20 @@
       <c r="F15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>29</v>
+      <c r="G15" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I15" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J15" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -1758,14 +1878,20 @@
       <c r="F16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>19</v>
+      <c r="G16" t="s">
+        <v>170</v>
+      </c>
+      <c r="H16" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I16" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J16" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K16" s="6">
         <v>3</v>
@@ -1787,14 +1913,20 @@
       <c r="F17" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>44</v>
+      <c r="G17" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 16GB</v>
+      </c>
+      <c r="I17" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J17" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>695000</v>
       </c>
       <c r="K17" s="6">
         <v>1</v>
@@ -1816,14 +1948,20 @@
       <c r="F18" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>19</v>
+      <c r="G18" t="s">
+        <v>172</v>
+      </c>
+      <c r="H18" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I18" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J18" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K18" s="6">
         <v>4</v>
@@ -1845,14 +1983,20 @@
       <c r="F19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>29</v>
+      <c r="G19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H19" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I19" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J19" s="6">
-        <v>350000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K19" s="6">
         <v>5</v>
@@ -1874,14 +2018,20 @@
       <c r="F20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>36</v>
+      <c r="G20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I20" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J20" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K20" s="6">
         <v>1</v>
@@ -1903,14 +2053,20 @@
       <c r="F21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>22</v>
+      <c r="G21" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I21" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J21" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K21" s="6">
         <v>3</v>
@@ -1932,14 +2088,20 @@
       <c r="F22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>22</v>
+      <c r="G22" t="s">
+        <v>176</v>
+      </c>
+      <c r="H22" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I22" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J22" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K22" s="6">
         <v>1</v>
@@ -1961,14 +2123,20 @@
       <c r="F23" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>39</v>
+      <c r="G23" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Cooling Pad</v>
+      </c>
+      <c r="I23" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J23" s="6">
-        <v>420000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K23" s="6">
         <v>3</v>
@@ -1990,14 +2158,20 @@
       <c r="F24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>29</v>
+      <c r="G24" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Harddisk External 1TB</v>
+      </c>
+      <c r="I24" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J24" s="6">
-        <v>220000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>950000</v>
       </c>
       <c r="K24" s="6">
         <v>2</v>
@@ -2019,14 +2193,20 @@
       <c r="F25" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>29</v>
+      <c r="G25" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Router TP-Link</v>
+      </c>
+      <c r="I25" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J25" s="6">
-        <v>275000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>420000</v>
       </c>
       <c r="K25" s="6">
         <v>5</v>
@@ -2048,14 +2228,20 @@
       <c r="F26" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>22</v>
+      <c r="G26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Switch 8 Port</v>
+      </c>
+      <c r="I26" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J26" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>390000</v>
       </c>
       <c r="K26" s="6">
         <v>2</v>
@@ -2077,14 +2263,20 @@
       <c r="F27" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>44</v>
+      <c r="G27" t="s">
+        <v>181</v>
+      </c>
+      <c r="H27" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>UPS 650VA</v>
+      </c>
+      <c r="I27" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Power</v>
       </c>
       <c r="J27" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>720000</v>
       </c>
       <c r="K27" s="6">
         <v>5</v>
@@ -2106,14 +2298,20 @@
       <c r="F28" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>29</v>
+      <c r="G28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Speaker Logitech Z120</v>
+      </c>
+      <c r="I28" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Audio</v>
       </c>
       <c r="J28" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>210000</v>
       </c>
       <c r="K28" s="6">
         <v>1</v>
@@ -2135,14 +2333,20 @@
       <c r="F29" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>29</v>
+      <c r="G29" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mousepad Gaming</v>
+      </c>
+      <c r="I29" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J29" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>75000</v>
       </c>
       <c r="K29" s="6">
         <v>3</v>
@@ -2164,14 +2368,20 @@
       <c r="F30" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>29</v>
+      <c r="G30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H30" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mouse Logitech M185</v>
+      </c>
+      <c r="I30" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J30" s="6">
-        <v>275000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K30" s="6">
         <v>2</v>
@@ -2193,14 +2403,20 @@
       <c r="F31" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>39</v>
+      <c r="G31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Keyboard Logitech K120</v>
+      </c>
+      <c r="I31" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J31" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K31" s="6">
         <v>4</v>
@@ -2222,14 +2438,20 @@
       <c r="F32" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>44</v>
+      <c r="G32" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Headset Fantech HG11</v>
+      </c>
+      <c r="I32" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J32" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>275000</v>
       </c>
       <c r="K32" s="6">
         <v>2</v>
@@ -2251,14 +2473,20 @@
       <c r="F33" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>26</v>
+      <c r="G33" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Flashdisk Sandisk 32GB</v>
+      </c>
+      <c r="I33" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J33" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>95000</v>
       </c>
       <c r="K33" s="6">
         <v>5</v>
@@ -2280,14 +2508,20 @@
       <c r="F34" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>26</v>
+      <c r="G34" t="s">
+        <v>169</v>
+      </c>
+      <c r="H34" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I34" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J34" s="6">
-        <v>460000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K34" s="6">
         <v>4</v>
@@ -2309,14 +2543,20 @@
       <c r="F35" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>22</v>
+      <c r="G35" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I35" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J35" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K35" s="6">
         <v>2</v>
@@ -2338,14 +2578,20 @@
       <c r="F36" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>29</v>
+      <c r="G36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 16GB</v>
+      </c>
+      <c r="I36" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J36" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>695000</v>
       </c>
       <c r="K36" s="6">
         <v>1</v>
@@ -2367,14 +2613,20 @@
       <c r="F37" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>36</v>
+      <c r="G37" t="s">
+        <v>172</v>
+      </c>
+      <c r="H37" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I37" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J37" s="6">
-        <v>385000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K37" s="6">
         <v>4</v>
@@ -2396,14 +2648,20 @@
       <c r="F38" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>29</v>
+      <c r="G38" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I38" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J38" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K38" s="6">
         <v>5</v>
@@ -2425,14 +2683,20 @@
       <c r="F39" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>44</v>
+      <c r="G39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H39" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I39" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J39" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K39" s="6">
         <v>5</v>
@@ -2454,14 +2718,20 @@
       <c r="F40" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>19</v>
+      <c r="G40" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I40" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J40" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K40" s="6">
         <v>5</v>
@@ -2483,14 +2753,20 @@
       <c r="F41" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>29</v>
+      <c r="G41" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I41" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J41" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K41" s="6">
         <v>1</v>
@@ -2512,14 +2788,20 @@
       <c r="F42" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>36</v>
+      <c r="G42" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Cooling Pad</v>
+      </c>
+      <c r="I42" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J42" s="6">
-        <v>385000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K42" s="6">
         <v>4</v>
@@ -2541,14 +2823,20 @@
       <c r="F43" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>44</v>
+      <c r="G43" t="s">
+        <v>178</v>
+      </c>
+      <c r="H43" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Harddisk External 1TB</v>
+      </c>
+      <c r="I43" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J43" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>950000</v>
       </c>
       <c r="K43" s="6">
         <v>5</v>
@@ -2570,14 +2858,20 @@
       <c r="F44" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>19</v>
+      <c r="G44" t="s">
+        <v>179</v>
+      </c>
+      <c r="H44" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Router TP-Link</v>
+      </c>
+      <c r="I44" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J44" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>420000</v>
       </c>
       <c r="K44" s="6">
         <v>3</v>
@@ -2599,14 +2893,20 @@
       <c r="F45" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I45" s="6" t="s">
-        <v>29</v>
+      <c r="G45" t="s">
+        <v>180</v>
+      </c>
+      <c r="H45" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Switch 8 Port</v>
+      </c>
+      <c r="I45" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J45" s="6">
-        <v>220000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>390000</v>
       </c>
       <c r="K45" s="6">
         <v>2</v>
@@ -2628,14 +2928,20 @@
       <c r="F46" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>29</v>
+      <c r="G46" t="s">
+        <v>181</v>
+      </c>
+      <c r="H46" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>UPS 650VA</v>
+      </c>
+      <c r="I46" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Power</v>
       </c>
       <c r="J46" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>720000</v>
       </c>
       <c r="K46" s="6">
         <v>4</v>
@@ -2657,14 +2963,20 @@
       <c r="F47" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>29</v>
+      <c r="G47" t="s">
+        <v>182</v>
+      </c>
+      <c r="H47" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Speaker Logitech Z120</v>
+      </c>
+      <c r="I47" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Audio</v>
       </c>
       <c r="J47" s="6">
-        <v>220000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>210000</v>
       </c>
       <c r="K47" s="6">
         <v>3</v>
@@ -2686,14 +2998,20 @@
       <c r="F48" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H48" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>22</v>
+      <c r="G48" t="s">
+        <v>183</v>
+      </c>
+      <c r="H48" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Microphone USB</v>
+      </c>
+      <c r="I48" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Audio</v>
       </c>
       <c r="J48" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>460000</v>
       </c>
       <c r="K48" s="6">
         <v>5</v>
@@ -2715,14 +3033,20 @@
       <c r="F49" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>39</v>
+      <c r="G49" t="s">
+        <v>184</v>
+      </c>
+      <c r="H49" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mousepad Gaming</v>
+      </c>
+      <c r="I49" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J49" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>75000</v>
       </c>
       <c r="K49" s="6">
         <v>1</v>
@@ -2744,14 +3068,20 @@
       <c r="F50" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>39</v>
+      <c r="G50" t="s">
+        <v>166</v>
+      </c>
+      <c r="H50" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mouse Logitech M185</v>
+      </c>
+      <c r="I50" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J50" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K50" s="6">
         <v>5</v>
@@ -2773,14 +3103,20 @@
       <c r="F51" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>32</v>
+      <c r="G51" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Keyboard Logitech K120</v>
+      </c>
+      <c r="I51" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J51" s="6">
-        <v>720000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K51" s="6">
         <v>5</v>
@@ -2802,14 +3138,20 @@
       <c r="F52" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="H52" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>36</v>
+      <c r="G52" t="s">
+        <v>168</v>
+      </c>
+      <c r="H52" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Headset Fantech HG11</v>
+      </c>
+      <c r="I52" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J52" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>275000</v>
       </c>
       <c r="K52" s="6">
         <v>5</v>
@@ -2831,14 +3173,20 @@
       <c r="F53" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>29</v>
+      <c r="G53" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Flashdisk Sandisk 32GB</v>
+      </c>
+      <c r="I53" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J53" s="6">
-        <v>350000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>95000</v>
       </c>
       <c r="K53" s="6">
         <v>4</v>
@@ -2860,14 +3208,20 @@
       <c r="F54" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="H54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>32</v>
+      <c r="G54" t="s">
+        <v>169</v>
+      </c>
+      <c r="H54" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I54" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J54" s="6">
-        <v>720000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K54" s="6">
         <v>4</v>
@@ -2889,14 +3243,20 @@
       <c r="F55" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="H55" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>22</v>
+      <c r="G55" t="s">
+        <v>170</v>
+      </c>
+      <c r="H55" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I55" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J55" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K55" s="6">
         <v>1</v>
@@ -2918,14 +3278,20 @@
       <c r="F56" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="H56" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>26</v>
+      <c r="G56" t="s">
+        <v>171</v>
+      </c>
+      <c r="H56" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 16GB</v>
+      </c>
+      <c r="I56" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J56" s="6">
-        <v>460000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>695000</v>
       </c>
       <c r="K56" s="6">
         <v>5</v>
@@ -2947,13 +3313,19 @@
       <c r="F57" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="H57" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>22</v>
+      <c r="G57" t="s">
+        <v>172</v>
+      </c>
+      <c r="H57" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I57" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J57" s="6">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
         <v>1850000</v>
       </c>
       <c r="K57" s="6">
@@ -2976,14 +3348,20 @@
       <c r="F58" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="H58" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>29</v>
+      <c r="G58" t="s">
+        <v>173</v>
+      </c>
+      <c r="H58" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I58" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J58" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K58" s="6">
         <v>2</v>
@@ -3005,14 +3383,20 @@
       <c r="F59" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="H59" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>29</v>
+      <c r="G59" t="s">
+        <v>174</v>
+      </c>
+      <c r="H59" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I59" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J59" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K59" s="6">
         <v>3</v>
@@ -3034,14 +3418,20 @@
       <c r="F60" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H60" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>22</v>
+      <c r="G60" t="s">
+        <v>175</v>
+      </c>
+      <c r="H60" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I60" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J60" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K60" s="6">
         <v>3</v>
@@ -3063,14 +3453,20 @@
       <c r="F61" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H61" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>26</v>
+      <c r="G61" t="s">
+        <v>176</v>
+      </c>
+      <c r="H61" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I61" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J61" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K61" s="6">
         <v>2</v>
@@ -3092,14 +3488,20 @@
       <c r="F62" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>39</v>
+      <c r="G62" t="s">
+        <v>177</v>
+      </c>
+      <c r="H62" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Cooling Pad</v>
+      </c>
+      <c r="I62" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J62" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K62" s="6">
         <v>4</v>
@@ -3121,14 +3523,20 @@
       <c r="F63" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>19</v>
+      <c r="G63" t="s">
+        <v>178</v>
+      </c>
+      <c r="H63" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Harddisk External 1TB</v>
+      </c>
+      <c r="I63" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J63" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>950000</v>
       </c>
       <c r="K63" s="6">
         <v>4</v>
@@ -3150,14 +3558,20 @@
       <c r="F64" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H64" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>19</v>
+      <c r="G64" t="s">
+        <v>179</v>
+      </c>
+      <c r="H64" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Router TP-Link</v>
+      </c>
+      <c r="I64" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J64" s="6">
-        <v>950000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>420000</v>
       </c>
       <c r="K64" s="6">
         <v>4</v>
@@ -3179,14 +3593,20 @@
       <c r="F65" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H65" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I65" s="6" t="s">
-        <v>19</v>
+      <c r="G65" t="s">
+        <v>180</v>
+      </c>
+      <c r="H65" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Switch 8 Port</v>
+      </c>
+      <c r="I65" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J65" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>390000</v>
       </c>
       <c r="K65" s="6">
         <v>1</v>
@@ -3208,14 +3628,20 @@
       <c r="F66" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>29</v>
+      <c r="G66" t="s">
+        <v>166</v>
+      </c>
+      <c r="H66" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mouse Logitech M185</v>
+      </c>
+      <c r="I66" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J66" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K66" s="6">
         <v>1</v>
@@ -3237,14 +3663,20 @@
       <c r="F67" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="H67" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>36</v>
+      <c r="G67" t="s">
+        <v>167</v>
+      </c>
+      <c r="H67" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Keyboard Logitech K120</v>
+      </c>
+      <c r="I67" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J67" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K67" s="6">
         <v>5</v>
@@ -3266,14 +3698,20 @@
       <c r="F68" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="H68" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I68" s="6" t="s">
-        <v>19</v>
+      <c r="G68" t="s">
+        <v>168</v>
+      </c>
+      <c r="H68" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Headset Fantech HG11</v>
+      </c>
+      <c r="I68" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J68" s="6">
-        <v>950000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>275000</v>
       </c>
       <c r="K68" s="6">
         <v>2</v>
@@ -3295,14 +3733,20 @@
       <c r="F69" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="H69" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>22</v>
+      <c r="G69" t="s">
+        <v>165</v>
+      </c>
+      <c r="H69" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Flashdisk Sandisk 32GB</v>
+      </c>
+      <c r="I69" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J69" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>95000</v>
       </c>
       <c r="K69" s="6">
         <v>1</v>
@@ -3324,14 +3768,20 @@
       <c r="F70" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H70" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>26</v>
+      <c r="G70" t="s">
+        <v>169</v>
+      </c>
+      <c r="H70" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I70" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J70" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K70" s="6">
         <v>1</v>
@@ -3353,14 +3803,20 @@
       <c r="F71" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H71" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I71" s="6" t="s">
-        <v>26</v>
+      <c r="G71" t="s">
+        <v>170</v>
+      </c>
+      <c r="H71" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I71" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J71" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K71" s="6">
         <v>1</v>
@@ -3382,14 +3838,20 @@
       <c r="F72" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>22</v>
+      <c r="G72" t="s">
+        <v>171</v>
+      </c>
+      <c r="H72" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 16GB</v>
+      </c>
+      <c r="I72" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J72" s="6">
-        <v>1850000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>695000</v>
       </c>
       <c r="K72" s="6">
         <v>2</v>
@@ -3411,14 +3873,20 @@
       <c r="F73" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H73" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I73" s="6" t="s">
-        <v>39</v>
+      <c r="G73" t="s">
+        <v>172</v>
+      </c>
+      <c r="H73" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I73" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J73" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K73" s="6">
         <v>2</v>
@@ -3440,14 +3908,20 @@
       <c r="F74" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="H74" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I74" s="6" t="s">
-        <v>29</v>
+      <c r="G74" t="s">
+        <v>173</v>
+      </c>
+      <c r="H74" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I74" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J74" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K74" s="6">
         <v>2</v>
@@ -3469,14 +3943,20 @@
       <c r="F75" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="H75" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>29</v>
+      <c r="G75" t="s">
+        <v>174</v>
+      </c>
+      <c r="H75" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I75" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J75" s="6">
-        <v>180000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K75" s="6">
         <v>3</v>
@@ -3498,14 +3978,20 @@
       <c r="F76" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H76" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>19</v>
+      <c r="G76" t="s">
+        <v>175</v>
+      </c>
+      <c r="H76" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I76" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J76" s="6">
-        <v>950000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K76" s="6">
         <v>5</v>
@@ -3527,14 +4013,20 @@
       <c r="F77" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>36</v>
+      <c r="G77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I77" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J77" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K77" s="6">
         <v>3</v>
@@ -3556,13 +4048,19 @@
       <c r="F78" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="H78" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>29</v>
+      <c r="G78" t="s">
+        <v>177</v>
+      </c>
+      <c r="H78" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Cooling Pad</v>
+      </c>
+      <c r="I78" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J78" s="6">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
         <v>180000</v>
       </c>
       <c r="K78" s="6">
@@ -3585,14 +4083,20 @@
       <c r="F79" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H79" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I79" s="6" t="s">
-        <v>29</v>
+      <c r="G79" t="s">
+        <v>178</v>
+      </c>
+      <c r="H79" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Harddisk External 1TB</v>
+      </c>
+      <c r="I79" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J79" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>950000</v>
       </c>
       <c r="K79" s="6">
         <v>1</v>
@@ -3614,14 +4118,20 @@
       <c r="F80" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="H80" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I80" s="6" t="s">
-        <v>39</v>
+      <c r="G80" t="s">
+        <v>179</v>
+      </c>
+      <c r="H80" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Router TP-Link</v>
+      </c>
+      <c r="I80" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J80" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>420000</v>
       </c>
       <c r="K80" s="6">
         <v>5</v>
@@ -3643,14 +4153,20 @@
       <c r="F81" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="H81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I81" s="6" t="s">
-        <v>32</v>
+      <c r="G81" t="s">
+        <v>180</v>
+      </c>
+      <c r="H81" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Switch 8 Port</v>
+      </c>
+      <c r="I81" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J81" s="6">
-        <v>720000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>390000</v>
       </c>
       <c r="K81" s="6">
         <v>1</v>
@@ -3672,14 +4188,20 @@
       <c r="F82" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="H82" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I82" s="6" t="s">
-        <v>29</v>
+      <c r="G82" t="s">
+        <v>166</v>
+      </c>
+      <c r="H82" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Mouse Logitech M185</v>
+      </c>
+      <c r="I82" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J82" s="6">
-        <v>75000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>125000</v>
       </c>
       <c r="K82" s="6">
         <v>1</v>
@@ -3701,14 +4223,20 @@
       <c r="F83" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="H83" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I83" s="6" t="s">
-        <v>19</v>
+      <c r="G83" t="s">
+        <v>167</v>
+      </c>
+      <c r="H83" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Keyboard Logitech K120</v>
+      </c>
+      <c r="I83" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J83" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K83" s="6">
         <v>5</v>
@@ -3730,14 +4258,20 @@
       <c r="F84" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="H84" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>29</v>
+      <c r="G84" t="s">
+        <v>168</v>
+      </c>
+      <c r="H84" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Headset Fantech HG11</v>
+      </c>
+      <c r="I84" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J84" s="6">
-        <v>75000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>275000</v>
       </c>
       <c r="K84" s="6">
         <v>1</v>
@@ -3759,14 +4293,20 @@
       <c r="F85" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="H85" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>26</v>
+      <c r="G85" t="s">
+        <v>165</v>
+      </c>
+      <c r="H85" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Flashdisk Sandisk 32GB</v>
+      </c>
+      <c r="I85" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J85" s="6">
-        <v>460000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>95000</v>
       </c>
       <c r="K85" s="6">
         <v>5</v>
@@ -3788,14 +4328,20 @@
       <c r="F86" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="H86" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>44</v>
+      <c r="G86" t="s">
+        <v>169</v>
+      </c>
+      <c r="H86" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>SSD Kingston 512GB</v>
+      </c>
+      <c r="I86" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J86" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>725000</v>
       </c>
       <c r="K86" s="6">
         <v>2</v>
@@ -3817,14 +4363,20 @@
       <c r="F87" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="H87" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>44</v>
+      <c r="G87" t="s">
+        <v>170</v>
+      </c>
+      <c r="H87" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 8GB</v>
+      </c>
+      <c r="I87" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J87" s="6">
-        <v>2450000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>385000</v>
       </c>
       <c r="K87" s="6">
         <v>4</v>
@@ -3846,14 +4398,20 @@
       <c r="F88" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="H88" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>29</v>
+      <c r="G88" t="s">
+        <v>171</v>
+      </c>
+      <c r="H88" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>RAM DDR4 16GB</v>
+      </c>
+      <c r="I88" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Komponen</v>
       </c>
       <c r="J88" s="6">
-        <v>350000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>695000</v>
       </c>
       <c r="K88" s="6">
         <v>4</v>
@@ -3875,14 +4433,20 @@
       <c r="F89" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H89" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>29</v>
+      <c r="G89" t="s">
+        <v>172</v>
+      </c>
+      <c r="H89" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I89" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J89" s="6">
-        <v>275000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K89" s="6">
         <v>1</v>
@@ -3904,14 +4468,20 @@
       <c r="F90" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="H90" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>26</v>
+      <c r="G90" t="s">
+        <v>173</v>
+      </c>
+      <c r="H90" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I90" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J90" s="6">
-        <v>460000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K90" s="6">
         <v>1</v>
@@ -3933,14 +4503,20 @@
       <c r="F91" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="H91" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>36</v>
+      <c r="G91" t="s">
+        <v>174</v>
+      </c>
+      <c r="H91" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I91" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J91" s="6">
-        <v>695000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K91" s="6">
         <v>5</v>
@@ -3962,14 +4538,20 @@
       <c r="F92" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H92" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>29</v>
+      <c r="G92" t="s">
+        <v>175</v>
+      </c>
+      <c r="H92" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I92" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J92" s="6">
-        <v>220000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K92" s="6">
         <v>1</v>
@@ -3991,14 +4573,20 @@
       <c r="F93" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H93" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>29</v>
+      <c r="G93" t="s">
+        <v>176</v>
+      </c>
+      <c r="H93" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I93" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J93" s="6">
-        <v>350000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K93" s="6">
         <v>2</v>
@@ -4020,14 +4608,20 @@
       <c r="F94" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="H94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>26</v>
+      <c r="G94" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Cooling Pad</v>
+      </c>
+      <c r="I94" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J94" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>180000</v>
       </c>
       <c r="K94" s="6">
         <v>3</v>
@@ -4049,14 +4643,20 @@
       <c r="F95" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="H95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>26</v>
+      <c r="G95" t="s">
+        <v>178</v>
+      </c>
+      <c r="H95" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Harddisk External 1TB</v>
+      </c>
+      <c r="I95" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Storage</v>
       </c>
       <c r="J95" s="6">
-        <v>210000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>950000</v>
       </c>
       <c r="K95" s="6">
         <v>3</v>
@@ -4078,14 +4678,20 @@
       <c r="F96" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H96" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>19</v>
+      <c r="G96" t="s">
+        <v>179</v>
+      </c>
+      <c r="H96" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Router TP-Link</v>
+      </c>
+      <c r="I96" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J96" s="6">
-        <v>725000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>420000</v>
       </c>
       <c r="K96" s="6">
         <v>3</v>
@@ -4107,14 +4713,20 @@
       <c r="F97" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="H97" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>19</v>
+      <c r="G97" t="s">
+        <v>180</v>
+      </c>
+      <c r="H97" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Switch 8 Port</v>
+      </c>
+      <c r="I97" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Networking</v>
       </c>
       <c r="J97" s="6">
-        <v>95000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>390000</v>
       </c>
       <c r="K97" s="6">
         <v>5</v>
@@ -4136,14 +4748,20 @@
       <c r="F98" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H98" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>29</v>
+      <c r="G98" t="s">
+        <v>181</v>
+      </c>
+      <c r="H98" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>UPS 650VA</v>
+      </c>
+      <c r="I98" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Power</v>
       </c>
       <c r="J98" s="6">
-        <v>350000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>720000</v>
       </c>
       <c r="K98" s="6">
         <v>5</v>
@@ -4165,14 +4783,20 @@
       <c r="F99" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="H99" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>29</v>
+      <c r="G99" t="s">
+        <v>182</v>
+      </c>
+      <c r="H99" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Speaker Logitech Z120</v>
+      </c>
+      <c r="I99" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Audio</v>
       </c>
       <c r="J99" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>210000</v>
       </c>
       <c r="K99" s="6">
         <v>2</v>
@@ -4194,14 +4818,20 @@
       <c r="F100" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="H100" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>39</v>
+      <c r="G100" t="s">
+        <v>183</v>
+      </c>
+      <c r="H100" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Microphone USB</v>
+      </c>
+      <c r="I100" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Audio</v>
       </c>
       <c r="J100" s="6">
-        <v>390000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>460000</v>
       </c>
       <c r="K100" s="6">
         <v>3</v>
@@ -4223,14 +4853,20 @@
       <c r="F101" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="H101" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>19</v>
+      <c r="G101" t="s">
+        <v>172</v>
+      </c>
+      <c r="H101" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Monitor LG 24"</v>
+      </c>
+      <c r="I101" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Monitor</v>
       </c>
       <c r="J101" s="6">
-        <v>950000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>1850000</v>
       </c>
       <c r="K101" s="6">
         <v>3</v>
@@ -4252,14 +4888,20 @@
       <c r="F102" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="H102" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>29</v>
+      <c r="G102" t="s">
+        <v>173</v>
+      </c>
+      <c r="H102" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Printer Epson L3250</v>
+      </c>
+      <c r="I102" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Printer</v>
       </c>
       <c r="J102" s="6">
-        <v>85000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>2450000</v>
       </c>
       <c r="K102" s="6">
         <v>2</v>
@@ -4281,14 +4923,20 @@
       <c r="F103" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="H103" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>39</v>
+      <c r="G103" t="s">
+        <v>174</v>
+      </c>
+      <c r="H103" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Webcam Logitech C270</v>
+      </c>
+      <c r="I103" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J103" s="6">
-        <v>420000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>350000</v>
       </c>
       <c r="K103" s="6">
         <v>5</v>
@@ -4310,14 +4958,20 @@
       <c r="F104" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="H104" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>29</v>
+      <c r="G104" t="s">
+        <v>175</v>
+      </c>
+      <c r="H104" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Kabel HDMI 2 Meter</v>
+      </c>
+      <c r="I104" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
       </c>
       <c r="J104" s="6">
-        <v>125000</v>
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>85000</v>
       </c>
       <c r="K104" s="6">
         <v>1</v>
@@ -4339,14 +4993,20 @@
       <c r="F105" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="H105" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="I105" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J105" s="7">
-        <v>725000</v>
+      <c r="G105" t="s">
+        <v>176</v>
+      </c>
+      <c r="H105" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
+        <v>Laptop Stand</v>
+      </c>
+      <c r="I105" s="6" t="str">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Kategori],"")</f>
+        <v>Aksesoris</v>
+      </c>
+      <c r="J105" s="6">
+        <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</f>
+        <v>220000</v>
       </c>
       <c r="K105" s="7">
         <v>5</v>
@@ -4362,6 +5022,7 @@
   <mergeCells count="1">
     <mergeCell ref="B3:C3"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G6:G105" xr:uid="{7DDB9F01-016C-40D1-9876-3AC073E4FF7E}">
       <formula1>KodeProduk</formula1>

--- a/Excel Junior.xlsx
+++ b/Excel Junior.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hani\Documents\Excel-Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A318B6-F761-433B-BCB2-B716CC9D68BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAE5F18-5A19-4A37-AE2E-7751D76226CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{3A5B9488-4C2F-4F4D-AD83-87F7C6430F9C}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="189">
   <si>
     <t>DATA PENJUALAN</t>
   </si>
@@ -83,9 +83,6 @@
     <t>Total Penjualan</t>
   </si>
   <si>
-    <t>Jumlah Transaksi</t>
-  </si>
-  <si>
     <t>Produk Terlaris</t>
   </si>
   <si>
@@ -600,6 +597,21 @@
   </si>
   <si>
     <t>PR020</t>
+  </si>
+  <si>
+    <t>Total Transaksi</t>
+  </si>
+  <si>
+    <t>Total Qty Terjual</t>
+  </si>
+  <si>
+    <t>Rata - Rata penjualan</t>
+  </si>
+  <si>
+    <t>Penjualan Tertinggi</t>
+  </si>
+  <si>
+    <t>Penjualan Terendah</t>
   </si>
 </sst>
 </file>
@@ -698,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -735,9 +747,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1174,7 +1183,9 @@
       <calculatedColumnFormula>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Harga],"")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{D0A2317B-0228-4B19-924B-8C05167BA4AE}" name="Qty" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{DD9C52D6-FDB5-46F9-803A-0E083341E491}" name="Diskon" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{DD9C52D6-FDB5-46F9-803A-0E083341E491}" name="Diskon" dataDxfId="2">
+      <calculatedColumnFormula>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="10" xr3:uid="{2809CFFE-8337-4F60-BBEB-44FE115319C6}" name="Total" dataDxfId="1">
       <calculatedColumnFormula>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</calculatedColumnFormula>
     </tableColumn>
@@ -1520,7 +1531,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -1528,7 +1539,7 @@
     <col min="10" max="10" width="12.5703125" style="5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -1541,14 +1552,14 @@
       <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>1</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>4</v>
@@ -1565,7 +1576,7 @@
       <c r="L5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="16" t="s">
+      <c r="M5" s="15" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1573,14 +1584,14 @@
       <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H6" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1598,25 +1609,26 @@
         <v>1</v>
       </c>
       <c r="L6" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M6" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>105000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>125000</v>
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D7" s="9">
         <v>2</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="19">
         <v>46241</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H7" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1634,25 +1646,26 @@
         <v>2</v>
       </c>
       <c r="L7" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M7" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>245000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>250000</v>
       </c>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D8" s="9">
         <v>3</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1670,25 +1683,26 @@
         <v>1</v>
       </c>
       <c r="L8" s="11">
-        <v>50000</v>
-      </c>
-      <c r="M8" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>45000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>95000</v>
       </c>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D9" s="9">
         <v>4</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="19">
         <v>46060</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H9" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1706,25 +1720,26 @@
         <v>1</v>
       </c>
       <c r="L9" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M9" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>710000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>725000</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D10" s="9">
         <v>5</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="19">
         <v>46241</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H10" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1742,25 +1757,26 @@
         <v>5</v>
       </c>
       <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1375000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M10" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1325000</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D11" s="9">
         <v>6</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>34</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H11" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1778,9 +1794,10 @@
         <v>5</v>
       </c>
       <c r="L11" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>1700000</v>
       </c>
@@ -1789,14 +1806,14 @@
       <c r="D12" s="9">
         <v>7</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="19">
         <v>46241</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H12" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1814,25 +1831,26 @@
         <v>5</v>
       </c>
       <c r="L12" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M12" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>405000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>425000</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D13" s="9">
         <v>8</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H13" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1850,9 +1868,10 @@
         <v>2</v>
       </c>
       <c r="L13" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>3650000</v>
       </c>
@@ -1861,14 +1880,14 @@
       <c r="D14" s="9">
         <v>9</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>46333</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H14" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1886,25 +1905,26 @@
         <v>2</v>
       </c>
       <c r="L14" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M14" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>755000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>770000</v>
       </c>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D15" s="9">
         <v>10</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>46</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H15" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1922,25 +1942,26 @@
         <v>1</v>
       </c>
       <c r="L15" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M15" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>720000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>725000</v>
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D16" s="9">
         <v>11</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H16" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1958,25 +1979,26 @@
         <v>3</v>
       </c>
       <c r="L16" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M16" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1130000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M16" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1105000</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D17" s="9">
         <v>12</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>51</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H17" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -1994,25 +2016,26 @@
         <v>1</v>
       </c>
       <c r="L17" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M17" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>595000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>695000</v>
       </c>
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D18" s="9">
         <v>13</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>33</v>
+      <c r="E18" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H18" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2030,25 +2053,26 @@
         <v>4</v>
       </c>
       <c r="L18" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M18" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>7395000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M18" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>7350000</v>
       </c>
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D19" s="9">
         <v>14</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>33</v>
+      <c r="E19" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H19" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2066,25 +2090,26 @@
         <v>5</v>
       </c>
       <c r="L19" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M19" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>12225000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M19" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>12200000</v>
       </c>
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D20" s="9">
         <v>15</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>56</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H20" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2102,9 +2127,10 @@
         <v>1</v>
       </c>
       <c r="L20" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>350000</v>
       </c>
@@ -2113,14 +2139,14 @@
       <c r="D21" s="9">
         <v>16</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>23</v>
+      <c r="E21" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H21" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2138,25 +2164,26 @@
         <v>3</v>
       </c>
       <c r="L21" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M21" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>250000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>255000</v>
       </c>
     </row>
     <row r="22" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D22" s="9">
         <v>17</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H22" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2174,25 +2201,26 @@
         <v>1</v>
       </c>
       <c r="L22" s="11">
-        <v>50000</v>
-      </c>
-      <c r="M22" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>170000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>220000</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D23" s="9">
         <v>18</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="19">
         <v>46272</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H23" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2210,25 +2238,26 @@
         <v>3</v>
       </c>
       <c r="L23" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M23" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>530000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>540000</v>
       </c>
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D24" s="9">
         <v>19</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="19">
         <v>46363</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H24" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2246,25 +2275,26 @@
         <v>2</v>
       </c>
       <c r="L24" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M24" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1880000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M24" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1850000</v>
       </c>
     </row>
     <row r="25" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D25" s="9">
         <v>20</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>64</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H25" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2282,25 +2312,26 @@
         <v>5</v>
       </c>
       <c r="L25" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M25" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2090000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M25" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2050000</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D26" s="9">
         <v>21</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>33</v>
+      <c r="E26" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H26" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2318,25 +2349,26 @@
         <v>2</v>
       </c>
       <c r="L26" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M26" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>680000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>780000</v>
       </c>
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D27" s="9">
         <v>22</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>48</v>
+      <c r="E27" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H27" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2354,25 +2386,26 @@
         <v>5</v>
       </c>
       <c r="L27" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M27" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>3585000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M27" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>3550000</v>
       </c>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" s="9">
         <v>23</v>
       </c>
-      <c r="E28" s="20" t="s">
-        <v>23</v>
+      <c r="E28" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H28" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2390,25 +2423,26 @@
         <v>1</v>
       </c>
       <c r="L28" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M28" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>195000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M28" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>210000</v>
       </c>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" s="9">
         <v>24</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H29" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2426,25 +2460,26 @@
         <v>3</v>
       </c>
       <c r="L29" s="11">
-        <v>50000</v>
-      </c>
-      <c r="M29" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>175000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>225000</v>
       </c>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" s="9">
         <v>25</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="19">
         <v>46272</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H30" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2462,25 +2497,26 @@
         <v>2</v>
       </c>
       <c r="L30" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M30" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>225000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>250000</v>
       </c>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D31" s="9">
         <v>26</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="19">
         <v>46210</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H31" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2498,25 +2534,26 @@
         <v>4</v>
       </c>
       <c r="L31" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M31" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>620000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>720000</v>
       </c>
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D32" s="9">
         <v>27</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="19">
         <v>46149</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H32" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2534,25 +2571,26 @@
         <v>2</v>
       </c>
       <c r="L32" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M32" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>535000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>550000</v>
       </c>
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D33" s="9">
         <v>28</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>77</v>
-      </c>
       <c r="G33" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H33" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2570,25 +2608,26 @@
         <v>5</v>
       </c>
       <c r="L33" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>455000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M33" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>475000</v>
       </c>
     </row>
     <row r="34" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D34" s="9">
         <v>29</v>
       </c>
-      <c r="E34" s="20" t="s">
-        <v>76</v>
+      <c r="E34" s="19" t="s">
+        <v>75</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H34" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2606,9 +2645,10 @@
         <v>4</v>
       </c>
       <c r="L34" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M34" s="17">
+      <c r="M34" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>2850000</v>
       </c>
@@ -2617,14 +2657,14 @@
       <c r="D35" s="9">
         <v>30</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="19">
         <v>46363</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H35" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2642,25 +2682,26 @@
         <v>2</v>
       </c>
       <c r="L35" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M35" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>670000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M35" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>770000</v>
       </c>
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D36" s="9">
         <v>31</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="19">
         <v>46088</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H36" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2678,25 +2719,26 @@
         <v>1</v>
       </c>
       <c r="L36" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M36" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>685000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>695000</v>
       </c>
     </row>
     <row r="37" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D37" s="9">
         <v>32</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>16</v>
+      <c r="E37" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H37" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2714,25 +2756,26 @@
         <v>4</v>
       </c>
       <c r="L37" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M37" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>7395000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M37" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>7350000</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D38" s="9">
         <v>33</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>48</v>
+      <c r="E38" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H38" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2750,25 +2793,26 @@
         <v>5</v>
       </c>
       <c r="L38" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M38" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>12150000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M38" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>12200000</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D39" s="9">
         <v>34</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>87</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H39" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2786,25 +2830,26 @@
         <v>5</v>
       </c>
       <c r="L39" s="11">
-        <v>0</v>
-      </c>
-      <c r="M39" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1750000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M39" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1700000</v>
       </c>
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D40" s="9">
         <v>35</v>
       </c>
-      <c r="E40" s="20" t="s">
-        <v>23</v>
+      <c r="E40" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H40" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2822,25 +2867,26 @@
         <v>5</v>
       </c>
       <c r="L40" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M40" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>405000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>425000</v>
       </c>
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D41" s="9">
         <v>36</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>90</v>
-      </c>
       <c r="G41" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H41" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2858,25 +2904,26 @@
         <v>1</v>
       </c>
       <c r="L41" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M41" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>200000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M41" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>220000</v>
       </c>
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D42" s="9">
         <v>37</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F42" s="10" t="s">
-        <v>92</v>
-      </c>
       <c r="G42" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H42" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2894,9 +2941,10 @@
         <v>4</v>
       </c>
       <c r="L42" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M42" s="17">
+      <c r="M42" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>720000</v>
       </c>
@@ -2905,14 +2953,14 @@
       <c r="D43" s="9">
         <v>38</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>45</v>
+      <c r="E43" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H43" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2930,25 +2978,26 @@
         <v>5</v>
       </c>
       <c r="L43" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M43" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>4740000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M43" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>4700000</v>
       </c>
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D44" s="9">
         <v>39</v>
       </c>
-      <c r="E44" s="20" t="s">
-        <v>86</v>
+      <c r="E44" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H44" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -2966,25 +3015,26 @@
         <v>3</v>
       </c>
       <c r="L44" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M44" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1245000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M44" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1210000</v>
       </c>
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D45" s="9">
         <v>40</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E45" s="19">
         <v>46149</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H45" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3002,9 +3052,10 @@
         <v>2</v>
       </c>
       <c r="L45" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M45" s="17">
+      <c r="M45" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>780000</v>
       </c>
@@ -3013,14 +3064,14 @@
       <c r="D46" s="9">
         <v>41</v>
       </c>
-      <c r="E46" s="20" t="s">
-        <v>50</v>
+      <c r="E46" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H46" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3038,25 +3089,26 @@
         <v>4</v>
       </c>
       <c r="L46" s="11">
-        <v>0</v>
-      </c>
-      <c r="M46" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2880000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M46" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2830000</v>
       </c>
     </row>
     <row r="47" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D47" s="9">
         <v>42</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E47" s="19">
         <v>46119</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H47" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3074,25 +3126,26 @@
         <v>3</v>
       </c>
       <c r="L47" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M47" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>615000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M47" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>630000</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D48" s="9">
         <v>43</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E48" s="19">
         <v>46060</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H48" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3110,25 +3163,26 @@
         <v>5</v>
       </c>
       <c r="L48" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M48" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2295000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M48" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2250000</v>
       </c>
     </row>
     <row r="49" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D49" s="9">
         <v>44</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E49" s="19">
         <v>46088</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H49" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3146,25 +3200,26 @@
         <v>1</v>
       </c>
       <c r="L49" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M49" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>65000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>75000</v>
       </c>
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D50" s="9">
         <v>45</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E50" s="19">
         <v>46149</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H50" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3182,25 +3237,26 @@
         <v>5</v>
       </c>
       <c r="L50" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M50" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>615000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M50" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>625000</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D51" s="9">
         <v>46</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E51" s="19">
         <v>46272</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H51" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3218,25 +3274,26 @@
         <v>5</v>
       </c>
       <c r="L51" s="11">
-        <v>50000</v>
-      </c>
-      <c r="M51" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>850000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M51" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D52" s="9">
         <v>47</v>
       </c>
-      <c r="E52" s="20" t="s">
-        <v>45</v>
+      <c r="E52" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H52" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3254,25 +3311,26 @@
         <v>5</v>
       </c>
       <c r="L52" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M52" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1360000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M52" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1325000</v>
       </c>
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D53" s="9">
         <v>48</v>
       </c>
-      <c r="E53" s="20" t="s">
-        <v>63</v>
+      <c r="E53" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H53" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3290,25 +3348,26 @@
         <v>4</v>
       </c>
       <c r="L53" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M53" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>355000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M53" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>380000</v>
       </c>
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D54" s="9">
         <v>49</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F54" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="F54" s="10" t="s">
-        <v>105</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H54" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3326,25 +3385,26 @@
         <v>4</v>
       </c>
       <c r="L54" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M54" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2895000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M54" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2850000</v>
       </c>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D55" s="9">
         <v>50</v>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="19">
         <v>46241</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H55" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3362,25 +3422,26 @@
         <v>1</v>
       </c>
       <c r="L55" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M55" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>360000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>385000</v>
       </c>
     </row>
     <row r="56" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D56" s="9">
         <v>51</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="19">
         <v>46029</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H56" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3398,25 +3459,26 @@
         <v>5</v>
       </c>
       <c r="L56" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M56" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>3460000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M56" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>3425000</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D57" s="9">
         <v>52</v>
       </c>
-      <c r="E57" s="20" t="s">
-        <v>55</v>
+      <c r="E57" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H57" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3434,25 +3496,26 @@
         <v>1</v>
       </c>
       <c r="L57" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M57" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1845000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M57" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1800000</v>
       </c>
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D58" s="9">
         <v>53</v>
       </c>
-      <c r="E58" s="20" t="s">
-        <v>63</v>
+      <c r="E58" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H58" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3470,25 +3533,26 @@
         <v>2</v>
       </c>
       <c r="L58" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M58" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>4895000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M58" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>4850000</v>
       </c>
     </row>
     <row r="59" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D59" s="9">
         <v>54</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F59" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="10" t="s">
-        <v>111</v>
-      </c>
       <c r="G59" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H59" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3506,25 +3570,26 @@
         <v>3</v>
       </c>
       <c r="L59" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M59" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1045000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M59" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D60" s="9">
         <v>55</v>
       </c>
-      <c r="E60" s="20" t="s">
-        <v>86</v>
+      <c r="E60" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H60" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3542,25 +3607,26 @@
         <v>3</v>
       </c>
       <c r="L60" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M60" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>155000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>255000</v>
       </c>
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D61" s="9">
         <v>56</v>
       </c>
-      <c r="E61" s="20">
+      <c r="E61" s="19">
         <v>46210</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H61" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3578,25 +3644,26 @@
         <v>2</v>
       </c>
       <c r="L61" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M61" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>340000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>440000</v>
       </c>
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D62" s="9">
         <v>57</v>
       </c>
-      <c r="E62" s="20">
+      <c r="E62" s="19">
         <v>46241</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H62" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3614,25 +3681,26 @@
         <v>4</v>
       </c>
       <c r="L62" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M62" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>705000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M62" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>720000</v>
       </c>
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D63" s="9">
         <v>58</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E63" s="19">
         <v>46119</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H63" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3650,25 +3718,26 @@
         <v>4</v>
       </c>
       <c r="L63" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M63" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>3775000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M63" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>3750000</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D64" s="9">
         <v>59</v>
       </c>
-      <c r="E64" s="20" t="s">
-        <v>91</v>
+      <c r="E64" s="19" t="s">
+        <v>90</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H64" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3686,25 +3755,26 @@
         <v>4</v>
       </c>
       <c r="L64" s="11">
-        <v>0</v>
-      </c>
-      <c r="M64" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1680000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M64" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1630000</v>
       </c>
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D65" s="9">
         <v>60</v>
       </c>
-      <c r="E65" s="20" t="s">
-        <v>23</v>
+      <c r="E65" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H65" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3722,25 +3792,26 @@
         <v>1</v>
       </c>
       <c r="L65" s="11">
-        <v>50000</v>
-      </c>
-      <c r="M65" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>340000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>390000</v>
       </c>
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D66" s="9">
         <v>61</v>
       </c>
-      <c r="E66" s="20" t="s">
-        <v>76</v>
+      <c r="E66" s="19" t="s">
+        <v>75</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H66" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3758,25 +3829,26 @@
         <v>1</v>
       </c>
       <c r="L66" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M66" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>110000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>125000</v>
       </c>
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D67" s="9">
         <v>62</v>
       </c>
-      <c r="E67" s="20">
+      <c r="E67" s="19">
         <v>46210</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H67" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3794,25 +3866,26 @@
         <v>5</v>
       </c>
       <c r="L67" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M67" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>800000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D68" s="9">
         <v>63</v>
       </c>
-      <c r="E68" s="20">
+      <c r="E68" s="19">
         <v>46149</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H68" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3830,25 +3903,26 @@
         <v>2</v>
       </c>
       <c r="L68" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M68" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>530000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M68" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>550000</v>
       </c>
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D69" s="9">
         <v>64</v>
       </c>
-      <c r="E69" s="20" t="s">
-        <v>104</v>
+      <c r="E69" s="19" t="s">
+        <v>103</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H69" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3866,25 +3940,26 @@
         <v>1</v>
       </c>
       <c r="L69" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M69" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>-5000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>95000</v>
       </c>
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D70" s="9">
         <v>65</v>
       </c>
-      <c r="E70" s="20" t="s">
-        <v>40</v>
+      <c r="E70" s="19" t="s">
+        <v>39</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H70" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3902,9 +3977,10 @@
         <v>1</v>
       </c>
       <c r="L70" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M70" s="17">
+      <c r="M70" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>725000</v>
       </c>
@@ -3913,14 +3989,14 @@
       <c r="D71" s="9">
         <v>66</v>
       </c>
-      <c r="E71" s="20" t="s">
-        <v>16</v>
+      <c r="E71" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H71" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3938,25 +4014,26 @@
         <v>1</v>
       </c>
       <c r="L71" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M71" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>380000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M71" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>385000</v>
       </c>
     </row>
     <row r="72" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D72" s="9">
         <v>67</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>126</v>
-      </c>
       <c r="G72" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H72" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -3974,9 +4051,10 @@
         <v>2</v>
       </c>
       <c r="L72" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M72" s="17">
+      <c r="M72" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>1340000</v>
       </c>
@@ -3985,14 +4063,14 @@
       <c r="D73" s="9">
         <v>68</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="G73" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H73" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4010,9 +4088,10 @@
         <v>2</v>
       </c>
       <c r="L73" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M73" s="17">
+      <c r="M73" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>3650000</v>
       </c>
@@ -4021,14 +4100,14 @@
       <c r="D74" s="9">
         <v>69</v>
       </c>
-      <c r="E74" s="20" t="s">
-        <v>110</v>
+      <c r="E74" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H74" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4046,9 +4125,10 @@
         <v>2</v>
       </c>
       <c r="L74" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M74" s="17">
+      <c r="M74" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>4850000</v>
       </c>
@@ -4057,14 +4137,14 @@
       <c r="D75" s="9">
         <v>70</v>
       </c>
-      <c r="E75" s="20">
+      <c r="E75" s="19">
         <v>46029</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H75" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4082,25 +4162,26 @@
         <v>3</v>
       </c>
       <c r="L75" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M75" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>950000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M75" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1000000</v>
       </c>
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D76" s="9">
         <v>71</v>
       </c>
-      <c r="E76" s="20">
+      <c r="E76" s="19">
         <v>46302</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H76" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4118,25 +4199,26 @@
         <v>5</v>
       </c>
       <c r="L76" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M76" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>325000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M76" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>425000</v>
       </c>
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D77" s="9">
         <v>72</v>
       </c>
-      <c r="E77" s="20">
+      <c r="E77" s="19">
         <v>46149</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H77" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4154,25 +4236,26 @@
         <v>3</v>
       </c>
       <c r="L77" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M77" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>645000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M77" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>660000</v>
       </c>
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D78" s="9">
         <v>73</v>
       </c>
-      <c r="E78" s="20" t="s">
-        <v>45</v>
+      <c r="E78" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H78" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4190,9 +4273,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M78" s="17">
+      <c r="M78" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>900000</v>
       </c>
@@ -4201,14 +4285,14 @@
       <c r="D79" s="9">
         <v>74</v>
       </c>
-      <c r="E79" s="20" t="s">
-        <v>76</v>
+      <c r="E79" s="19" t="s">
+        <v>75</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H79" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4226,9 +4310,10 @@
         <v>1</v>
       </c>
       <c r="L79" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M79" s="17">
+      <c r="M79" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>950000</v>
       </c>
@@ -4237,14 +4322,14 @@
       <c r="D80" s="9">
         <v>75</v>
       </c>
-      <c r="E80" s="20" t="s">
-        <v>55</v>
+      <c r="E80" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H80" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4262,25 +4347,26 @@
         <v>5</v>
       </c>
       <c r="L80" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M80" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2090000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M80" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2050000</v>
       </c>
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D81" s="9">
         <v>76</v>
       </c>
-      <c r="E81" s="20">
+      <c r="E81" s="19">
         <v>46060</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H81" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4298,25 +4384,26 @@
         <v>1</v>
       </c>
       <c r="L81" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M81" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>380000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M81" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>390000</v>
       </c>
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D82" s="9">
         <v>77</v>
       </c>
-      <c r="E82" s="20">
+      <c r="E82" s="19">
         <v>46088</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H82" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4334,25 +4421,26 @@
         <v>1</v>
       </c>
       <c r="L82" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M82" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>110000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M82" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>125000</v>
       </c>
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D83" s="9">
         <v>78</v>
       </c>
-      <c r="E83" s="20" t="s">
-        <v>48</v>
+      <c r="E83" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H83" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4370,25 +4458,26 @@
         <v>5</v>
       </c>
       <c r="L83" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M83" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>885000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M83" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>900000</v>
       </c>
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D84" s="9">
         <v>79</v>
       </c>
-      <c r="E84" s="20" t="s">
-        <v>55</v>
+      <c r="E84" s="19" t="s">
+        <v>54</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H84" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4406,25 +4495,26 @@
         <v>1</v>
       </c>
       <c r="L84" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M84" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>270000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M84" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>275000</v>
       </c>
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D85" s="9">
         <v>80</v>
       </c>
-      <c r="E85" s="20" t="s">
-        <v>91</v>
+      <c r="E85" s="19" t="s">
+        <v>90</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H85" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4442,25 +4532,26 @@
         <v>5</v>
       </c>
       <c r="L85" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M85" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>450000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M85" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>475000</v>
       </c>
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D86" s="9">
         <v>81</v>
       </c>
-      <c r="E86" s="20" t="s">
-        <v>125</v>
+      <c r="E86" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H86" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4478,25 +4569,26 @@
         <v>2</v>
       </c>
       <c r="L86" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M86" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1425000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M86" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1400000</v>
       </c>
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D87" s="9">
         <v>82</v>
       </c>
-      <c r="E87" s="20">
+      <c r="E87" s="19">
         <v>46241</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H87" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4514,25 +4606,26 @@
         <v>4</v>
       </c>
       <c r="L87" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M87" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1530000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M87" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1490000</v>
       </c>
     </row>
     <row r="88" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D88" s="9">
         <v>83</v>
       </c>
-      <c r="E88" s="20" t="s">
-        <v>23</v>
+      <c r="E88" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H88" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4550,25 +4643,26 @@
         <v>4</v>
       </c>
       <c r="L88" s="11">
-        <v>25000</v>
-      </c>
-      <c r="M88" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2755000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M88" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2730000</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D89" s="9">
         <v>84</v>
       </c>
-      <c r="E89" s="20" t="s">
-        <v>125</v>
+      <c r="E89" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H89" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4586,25 +4680,26 @@
         <v>1</v>
       </c>
       <c r="L89" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M89" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1750000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M89" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1800000</v>
       </c>
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D90" s="9">
         <v>85</v>
       </c>
-      <c r="E90" s="20" t="s">
-        <v>50</v>
+      <c r="E90" s="19" t="s">
+        <v>49</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H90" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4622,25 +4717,26 @@
         <v>1</v>
       </c>
       <c r="L90" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M90" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2445000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M90" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2400000</v>
       </c>
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D91" s="9">
         <v>86</v>
       </c>
-      <c r="E91" s="20" t="s">
-        <v>33</v>
+      <c r="E91" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H91" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4658,25 +4754,26 @@
         <v>5</v>
       </c>
       <c r="L91" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M91" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1730000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M91" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1700000</v>
       </c>
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D92" s="9">
         <v>87</v>
       </c>
-      <c r="E92" s="20">
+      <c r="E92" s="19">
         <v>46149</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H92" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4694,25 +4791,26 @@
         <v>1</v>
       </c>
       <c r="L92" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M92" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>70000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M92" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>85000</v>
       </c>
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D93" s="9">
         <v>88</v>
       </c>
-      <c r="E93" s="20">
+      <c r="E93" s="19">
         <v>46363</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H93" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4730,25 +4828,26 @@
         <v>2</v>
       </c>
       <c r="L93" s="11">
-        <v>100000</v>
-      </c>
-      <c r="M93" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>340000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M93" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>440000</v>
       </c>
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D94" s="9">
         <v>89</v>
       </c>
-      <c r="E94" s="20" t="s">
-        <v>69</v>
+      <c r="E94" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H94" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4766,9 +4865,10 @@
         <v>3</v>
       </c>
       <c r="L94" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>0</v>
       </c>
-      <c r="M94" s="17">
+      <c r="M94" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>540000</v>
       </c>
@@ -4777,14 +4877,14 @@
       <c r="D95" s="9">
         <v>90</v>
       </c>
-      <c r="E95" s="20" t="s">
-        <v>23</v>
+      <c r="E95" s="19" t="s">
+        <v>22</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H95" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4802,25 +4902,26 @@
         <v>3</v>
       </c>
       <c r="L95" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M95" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>2845000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M95" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>2800000</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D96" s="9">
         <v>91</v>
       </c>
-      <c r="E96" s="20" t="s">
-        <v>45</v>
+      <c r="E96" s="19" t="s">
+        <v>44</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H96" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4838,25 +4939,26 @@
         <v>3</v>
       </c>
       <c r="L96" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M96" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1255000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M96" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1210000</v>
       </c>
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D97" s="9">
         <v>92</v>
       </c>
-      <c r="E97" s="20" t="s">
-        <v>110</v>
+      <c r="E97" s="19" t="s">
+        <v>109</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H97" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4874,25 +4976,26 @@
         <v>5</v>
       </c>
       <c r="L97" s="11">
-        <v>10000</v>
-      </c>
-      <c r="M97" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1940000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M97" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1900000</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D98" s="9">
         <v>93</v>
       </c>
-      <c r="E98" s="20">
+      <c r="E98" s="19">
         <v>46272</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H98" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4910,25 +5013,26 @@
         <v>5</v>
       </c>
       <c r="L98" s="11">
-        <v>15000</v>
-      </c>
-      <c r="M98" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>3585000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M98" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>3550000</v>
       </c>
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D99" s="9">
         <v>94</v>
       </c>
-      <c r="E99" s="20" t="s">
-        <v>63</v>
+      <c r="E99" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H99" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4946,25 +5050,26 @@
         <v>2</v>
       </c>
       <c r="L99" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M99" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>400000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M99" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>420000</v>
       </c>
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D100" s="9">
         <v>95</v>
       </c>
-      <c r="E100" s="20" t="s">
-        <v>86</v>
+      <c r="E100" s="19" t="s">
+        <v>85</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H100" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -4982,25 +5087,26 @@
         <v>3</v>
       </c>
       <c r="L100" s="11">
-        <v>0</v>
-      </c>
-      <c r="M100" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1380000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M100" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1330000</v>
       </c>
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D101" s="9">
         <v>96</v>
       </c>
-      <c r="E101" s="20">
+      <c r="E101" s="19">
         <v>46088</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H101" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -5018,25 +5124,26 @@
         <v>3</v>
       </c>
       <c r="L101" s="11">
-        <v>0</v>
-      </c>
-      <c r="M101" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>5550000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M101" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>5500000</v>
       </c>
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D102" s="9">
         <v>97</v>
       </c>
-      <c r="E102" s="20">
+      <c r="E102" s="19">
         <v>46029</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H102" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -5054,25 +5161,26 @@
         <v>2</v>
       </c>
       <c r="L102" s="11">
-        <v>20000</v>
-      </c>
-      <c r="M102" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>4880000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M102" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>4850000</v>
       </c>
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D103" s="9">
         <v>98</v>
       </c>
-      <c r="E103" s="20">
+      <c r="E103" s="19">
         <v>46180</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H103" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -5090,9 +5198,10 @@
         <v>5</v>
       </c>
       <c r="L103" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
         <v>50000</v>
       </c>
-      <c r="M103" s="17">
+      <c r="M103" s="16">
         <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
         <v>1700000</v>
       </c>
@@ -5101,14 +5210,14 @@
       <c r="D104" s="9">
         <v>99</v>
       </c>
-      <c r="E104" s="20" t="s">
-        <v>33</v>
+      <c r="E104" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H104" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -5126,25 +5235,26 @@
         <v>1</v>
       </c>
       <c r="L104" s="11">
-        <v>5000</v>
-      </c>
-      <c r="M104" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>80000</v>
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M104" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>85000</v>
       </c>
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D105" s="12">
         <v>100</v>
       </c>
-      <c r="E105" s="21" t="s">
-        <v>45</v>
+      <c r="E105" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="F105" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H105" s="10" t="str">
         <f>_xlfn.XLOOKUP(tblPenjualan[[#This Row],[Kode Produk]],tblProduk[Kode Produk],tblProduk[Produk],"")</f>
@@ -5161,12 +5271,13 @@
       <c r="K105" s="13">
         <v>5</v>
       </c>
-      <c r="L105" s="14">
-        <v>0</v>
-      </c>
-      <c r="M105" s="17">
-        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
-        <v>1100000</v>
+      <c r="L105" s="11">
+        <f>IF(tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]&gt;=1000000,50000,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="M105" s="16">
+        <f>tblPenjualan[[#This Row],[Harga]]*tblPenjualan[[#This Row],[Qty]]-tblPenjualan[[#This Row],[Diskon]]</f>
+        <v>1050000</v>
       </c>
     </row>
   </sheetData>
@@ -5199,7 +5310,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2" s="4"/>
     </row>
@@ -5208,7 +5319,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
@@ -5229,10 +5340,10 @@
         <v>PR001</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="H4" s="1">
         <v>125000</v>
@@ -5247,10 +5358,10 @@
         <v>PR002</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1">
         <v>180000</v>
@@ -5265,10 +5376,10 @@
         <v>PR003</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1">
         <v>275000</v>
@@ -5283,10 +5394,10 @@
         <v>PR004</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H7" s="1">
         <v>95000</v>
@@ -5301,10 +5412,10 @@
         <v>PR005</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1">
         <v>725000</v>
@@ -5319,10 +5430,10 @@
         <v>PR006</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1">
         <v>385000</v>
@@ -5337,10 +5448,10 @@
         <v>PR007</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="H10" s="1">
         <v>695000</v>
@@ -5355,10 +5466,10 @@
         <v>PR008</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="H11" s="1">
         <v>1850000</v>
@@ -5373,10 +5484,10 @@
         <v>PR009</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="H12" s="1">
         <v>2450000</v>
@@ -5391,10 +5502,10 @@
         <v>PR010</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" s="1">
         <v>350000</v>
@@ -5409,10 +5520,10 @@
         <v>PR011</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H14" s="1">
         <v>85000</v>
@@ -5427,10 +5538,10 @@
         <v>PR012</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H15" s="1">
         <v>220000</v>
@@ -5445,10 +5556,10 @@
         <v>PR013</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" s="1">
         <v>180000</v>
@@ -5463,10 +5574,10 @@
         <v>PR014</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="1">
         <v>950000</v>
@@ -5481,10 +5592,10 @@
         <v>PR015</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="H18" s="1">
         <v>420000</v>
@@ -5499,10 +5610,10 @@
         <v>PR016</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H19" s="1">
         <v>390000</v>
@@ -5517,10 +5628,10 @@
         <v>PR017</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="H20" s="1">
         <v>720000</v>
@@ -5535,10 +5646,10 @@
         <v>PR018</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="H21" s="1">
         <v>210000</v>
@@ -5553,10 +5664,10 @@
         <v>PR019</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H22" s="1">
         <v>460000</v>
@@ -5571,10 +5682,10 @@
         <v>PR020</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="1">
         <v>75000</v>
@@ -5598,43 +5709,80 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E408928-F670-4389-91FC-A42611E7F6CC}">
-  <dimension ref="B3:H5"/>
+  <dimension ref="B3:M9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>185</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="I4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D5" s="5">
         <f>SUM(tblPenjualan[Total])</f>
-        <v>164550000</v>
+        <v>165045000</v>
+      </c>
+      <c r="E5">
+        <f>COUNTA(tblPenjualan[Invoice])</f>
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <f>SUM(tblPenjualan[Qty])</f>
+        <v>296</v>
+      </c>
+      <c r="G5" s="5">
+        <f>AVERAGE(tblPenjualan[Total])</f>
+        <v>1650450</v>
+      </c>
+      <c r="H5">
+        <f>MAX(tblPenjualan[Total])</f>
+        <v>12200000</v>
+      </c>
+      <c r="I5">
+        <f>MIN(tblPenjualan[Total])</f>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
